--- a/uat-test-plans-reduced30/G2-16477-shipping-address.xlsx
+++ b/uat-test-plans-reduced30/G2-16477-shipping-address.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced ~25% — 9/12 checks retained, lowest-priority sections dropped] 27 UI-testable stories mapped to 12 business checks and 27 coverage rows. 10 non-UI/backend/evaluation stories are excluded from direct business execution.</t>
+          <t>[Reduced V2 ~17% — 10/12 checks retained; AC and core-case coverage guardrails enforced] 27 UI-testable stories mapped to 12 business checks and 27 coverage rows. 10 non-UI/backend/evaluation stories are excluded from direct business execution.</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=21097; payload_chars=21095; est_tokens~5274; checklist_rows=9; matrix_rows=24; exploratory_rows=3</t>
+          <t>payload_bytes=22968; payload_chars=22966; est_tokens~5742; checklist_rows=10; matrix_rows=27; exploratory_rows=3</t>
         </is>
       </c>
     </row>
@@ -731,12 +731,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
@@ -1069,7 +1069,7 @@
     <row r="10" ht="64" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>UAT-009</t>
+          <t>UAT-010</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1079,27 +1079,62 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Trimming and Input Hygiene</t>
+          <t>Checkout Routing</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Invisible characters and trimming are handled safely</t>
+          <t>Continue/back routing in shipping step preserves state</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Paste values with extra spaces/invisible characters in address fields and submit.</t>
+          <t>Use continue/back actions around shipping step, including redirect edge cases, and re-open shipping step.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Values are sanitized according to rules without corrupting user intent.
-Validation outcome is consistent after trimming.</t>
+          <t>Navigation does not lose valid address state unexpectedly.
+Customer returns to the expected checkout step.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
       <c r="H10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="64" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>UAT-012</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Cavazzuti, Matilde || LuxExperience</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Address Save and Duplication Guard</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Saving behavior avoids accidental duplicate addresses</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Submit same logical address multiple times through add/edit paths and inspect resulting address book/selection list.</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>No unintended duplicate address entries are introduced by checkout flow.
+Order proceeds with the intended selected address.</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1112,7 +1147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1815,22 +1850,22 @@
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>COV-013</t>
+          <t>COV-012</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>G2-21951</t>
+          <t>G2-22590</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>AC-G2-21951</t>
+          <t>AC-G2-22590</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Address Form Skeleton and SSR</t>
+          <t>Prevent Saving Duplicated Address In Shipping Address Step</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1840,12 +1875,12 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>UAT-001</t>
+          <t>UAT-012</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Inferred</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -1865,29 +1900,29 @@
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>Acceptance criteria are sparse or absent; behavior inferred from story goal/title.</t>
+          <t>No explicit conflict detected; some stories provide limited edge-case detail.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>COV-014</t>
+          <t>COV-013</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>G2-21547</t>
+          <t>G2-21951</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AC-G2-21547</t>
+          <t>AC-G2-21951</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Address Autocompletion</t>
+          <t>Address Form Skeleton and SSR</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1897,12 +1932,12 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>UAT-006</t>
+          <t>UAT-001</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Inferred</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -1922,29 +1957,29 @@
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>No explicit conflict detected; some stories provide limited edge-case detail.</t>
+          <t>Acceptance criteria are sparse or absent; behavior inferred from story goal/title.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>COV-015</t>
+          <t>COV-014</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>G2-19646</t>
+          <t>G2-21547</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AC-G2-19646</t>
+          <t>AC-G2-21547</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Address Form Fields Validation</t>
+          <t>Address Autocompletion</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1954,12 +1989,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>UAT-005</t>
+          <t>UAT-006</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Inferred</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -1979,39 +2014,39 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>Acceptance criteria are sparse or absent; behavior inferred from story goal/title.</t>
+          <t>No explicit conflict detected; some stories provide limited edge-case detail.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>COV-016</t>
+          <t>COV-015</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>G2-19645</t>
+          <t>G2-19646</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>AC-G2-19645</t>
+          <t>AC-G2-19646</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Address Form Fields Rendering</t>
+          <t>Address Form Fields Validation</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>UAT-001</t>
+          <t>UAT-005</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -2043,22 +2078,22 @@
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>COV-017</t>
+          <t>COV-016</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>G2-19644</t>
+          <t>G2-19645</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>AC-G2-19644</t>
+          <t>AC-G2-19645</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Address Form Data Model Integration</t>
+          <t>Address Form Fields Rendering</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2100,22 +2135,22 @@
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>COV-018</t>
+          <t>COV-017</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>G2-19343</t>
+          <t>G2-19644</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AC-G2-19343</t>
+          <t>AC-G2-19644</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Remove house number splitting</t>
+          <t>Address Form Data Model Integration</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2130,7 +2165,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Inferred</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -2150,29 +2185,29 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>No explicit conflict detected; some stories provide limited edge-case detail.</t>
+          <t>Acceptance criteria are sparse or absent; behavior inferred from story goal/title.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>COV-019</t>
+          <t>COV-018</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>G2-19222</t>
+          <t>G2-19343</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>AC-G2-19222</t>
+          <t>AC-G2-19343</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Fix select component's responsive height</t>
+          <t>Remove house number splitting</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -2214,32 +2249,32 @@
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>COV-020</t>
+          <t>COV-019</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>G2-19115</t>
+          <t>G2-19222</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AC-G2-19115</t>
+          <t>AC-G2-19222</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Edit Shipping Address</t>
+          <t>Fix select component's responsive height</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>UAT-004</t>
+          <t>UAT-001</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -2271,22 +2306,22 @@
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>COV-021</t>
+          <t>COV-020</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>G2-19114</t>
+          <t>G2-19115</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>AC-G2-19114</t>
+          <t>AC-G2-19115</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Shipping Address selection</t>
+          <t>Edit Shipping Address</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2296,7 +2331,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>UAT-003</t>
+          <t>UAT-004</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -2328,22 +2363,22 @@
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>COV-022</t>
+          <t>COV-021</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>G2-19113</t>
+          <t>G2-19114</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AC-G2-19113</t>
+          <t>AC-G2-19114</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Shipping Address Country</t>
+          <t>Shipping Address selection</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -2353,7 +2388,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>UAT-002</t>
+          <t>UAT-003</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -2385,37 +2420,37 @@
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>COV-023</t>
+          <t>COV-022</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>G2-18989</t>
+          <t>G2-19113</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>AC-G2-18989</t>
+          <t>AC-G2-19113</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Small Misalignments of Atelier vs MRP&amp;NAR real impl.</t>
+          <t>Shipping Address Country</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>UAT-001</t>
+          <t>UAT-002</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Inferred</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -2435,39 +2470,39 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>Acceptance criteria are sparse or absent; behavior inferred from story goal/title.</t>
+          <t>No explicit conflict detected; some stories provide limited edge-case detail.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="34" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>COV-024</t>
+          <t>COV-023</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>G2-18988</t>
+          <t>G2-18989</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>AC-G2-18988</t>
+          <t>AC-G2-18989</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Invisible characters - Extended trimming for shipping address validation.</t>
+          <t>Small Misalignments of Atelier vs MRP&amp;NAR real impl.</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>UAT-005</t>
+          <t>UAT-001</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -2499,55 +2534,226 @@
     <row r="25" ht="34" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>COV-024</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>G2-18988</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>AC-G2-18988</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Invisible characters - Extended trimming for shipping address validation.</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>UAT-005</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Jira description/comments/issuelinks scan: no GitHub PR/commit URL found</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>Acceptance criteria are sparse or absent; behavior inferred from story goal/title.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>COV-025</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>G2-18559</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>AC-G2-18559</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>"Continue to checkout" btn redirect screen movement</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>UAT-010</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Jira description/comments/issuelinks scan: no GitHub PR/commit URL found</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>Acceptance criteria are sparse or absent; behavior inferred from story goal/title.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>COV-026</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>G2-17909</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>AC-G2-17909</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Checkout route logic</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>UAT-010</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Jira description/comments/issuelinks scan: no GitHub PR/commit URL found</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>Acceptance criteria are sparse or absent; behavior inferred from story goal/title.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
           <t>COV-027</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>G2-17569</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>AC-G2-17569</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Shipping Address form (dynamic)</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>UAT-002</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>Inferred</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>Jira description/comments/issuelinks scan: no GitHub PR/commit URL found</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>Unavailable</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>Acceptance criteria are sparse or absent; behavior inferred from story goal/title.</t>
         </is>

--- a/uat-test-plans-reduced30/G2-16477-shipping-address.xlsx
+++ b/uat-test-plans-reduced30/G2-16477-shipping-address.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced V2 ~17% — 10/12 checks retained; AC and core-case coverage guardrails enforced] 27 UI-testable stories mapped to 12 business checks and 27 coverage rows. 10 non-UI/backend/evaluation stories are excluded from direct business execution.</t>
+          <t>[Reduced V2 ~17% — 10/12 checks retained; AC coverage guardrail enforced] 27 UI-testable stories mapped to 12 business checks and 27 coverage rows. 10 non-UI/backend/evaluation stories are excluded from direct business execution.</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=22968; payload_chars=22966; est_tokens~5742; checklist_rows=10; matrix_rows=27; exploratory_rows=3</t>
+          <t>payload_bytes=22953; payload_chars=22951; est_tokens~5738; checklist_rows=10; matrix_rows=27; exploratory_rows=3</t>
         </is>
       </c>
     </row>
